--- a/sales_analysis_march_w2.xlsx
+++ b/sales_analysis_march_w2.xlsx
@@ -20,7 +20,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bonface_Muriu" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lewis" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bonface_Kitheka" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WALK_IN-BOMAS" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -309,12 +308,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Rep Performance'!$B$4:$B$11</f>
+              <f>'Rep Performance'!$B$4:$B$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Rep Performance'!$D$4:$D$11</f>
+              <f>'Rep Performance'!$D$4:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -333,12 +332,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Rep Performance'!$B$4:$B$11</f>
+              <f>'Rep Performance'!$B$4:$B$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Rep Performance'!$E$4:$E$11</f>
+              <f>'Rep Performance'!$E$4:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -445,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'GENERAL HARDWAR'!$A$6:$A$13</f>
+              <f>'GENERAL HARDWAR'!$A$6:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GENERAL HARDWAR'!$B$6:$B$13</f>
+              <f>'GENERAL HARDWAR'!$B$6:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +502,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'PAINTS'!$A$6:$A$13</f>
+              <f>'PAINTS'!$A$6:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'PAINTS'!$B$6:$B$13</f>
+              <f>'PAINTS'!$B$6:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -619,12 +618,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ELECTRICALS'!$A$6:$A$13</f>
+              <f>'ELECTRICALS'!$A$6:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ELECTRICALS'!$B$6:$B$13</f>
+              <f>'ELECTRICALS'!$B$6:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -646,7 +645,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="4320000"/>
@@ -673,7 +672,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="3600000"/>
@@ -700,7 +699,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="3600000"/>
@@ -754,7 +753,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="3600000"/>
@@ -1066,14 +1065,6 @@
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1166,7 +1157,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Week 2 Actual</t>
+          <t>Cumulative Actual</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1195,17 +1186,17 @@
         <v>48500000</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>13630490</v>
+        <v>24078098</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.2810410309278351</v>
+        <v>0.4964556288659794</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Behind</t>
         </is>
       </c>
     </row>
@@ -1219,13 +1210,13 @@
         <v>7000000</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1339340</v>
+        <v>2209155</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.1913342857142857</v>
+        <v>0.3155935714285714</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
@@ -1243,13 +1234,13 @@
         <v>3000000</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>442175</v>
+        <v>1069723</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.1473916666666667</v>
+        <v>0.3565743333333333</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -1267,13 +1258,13 @@
         <v>1500000</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>163800</v>
+        <v>506890</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.1092</v>
+        <v>0.3379266666666667</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -1291,17 +1282,17 @@
         <v>60000000</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>15575805</v>
+        <v>27863866</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.25959675</v>
+        <v>0.4643977666666667</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Behind</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1383,145 +1374,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Performance Notes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>1721950</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>162444.7528</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.09433767112866226</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>2385.5</v>
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales 20% below team average - needs improvement</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>48610</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>10187.8972</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.209584390043201</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>58</v>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Margin at 9.8% below team average of 14.2%</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PLUMBING</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>180.0088</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.6000293333333334</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>6</v>
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  General Hardware: 12.6% of dept, 9.4% margin</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>12.4584</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.124584</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales 9% below team average - needs improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Margin at 9.8% below team average of 14.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  General Hardware: 12.6% of dept, 9.4% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Selling across all 4 categories - excellent product range</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Best margin in PLUMBING: 60.0%</t>
         </is>
@@ -1541,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1604,145 +1492,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Performance Notes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>139895</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>41838.0564</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.2990675606705029</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>256</v>
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales 45% below team average - needs improvement</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>1075980</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>196327.9932</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.18246435175375</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>851</v>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Excellent margin at 19.6% (Team avg: 14.2%)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PLUMBING</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>88.8676</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.3554704</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>1</v>
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Paints Dept Head: 80.3% of dept sales, 18.2% margin</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>1570</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>280.198</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.1784700636942675</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales 37% below team average - needs improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Excellent margin at 19.6% (Team avg: 14.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Paints Dept Head: 80.3% of dept sales, 18.2% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Good paints leadership with 80.3% of dept sales</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Selling across all 4 categories - excellent product range</t>
         </is>
@@ -1762,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1825,145 +1610,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Performance Notes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>72915</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>11921.4824</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.1634983528766372</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>261.5</v>
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales 78% below team average - needs improvement</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>30290</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>7479.6684</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.2469352393529217</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>45</v>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Excellent margin at 23.2% (Team avg: 14.2%)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PLUMBING</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>369615</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>90467.23999999999</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.2447607375241805</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>1201</v>
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Plumbing Dept Head: 83.6% of dept sales, 24.5% margin</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>6220</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>1318.166</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.2119237942122186</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales 75% below team average - needs improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Excellent margin at 23.2% (Team avg: 14.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Plumbing Dept Head: 83.6% of dept sales, 24.5% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Strong plumbing leadership with 83.6% of dept sales</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Selling across all 4 categories - excellent product range</t>
         </is>
@@ -1983,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2053,145 +1735,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Performance Notes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>84825</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>25098.6184</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.2958870427350427</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>3</v>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales 89% below team average - needs improvement</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>16000</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>3452.7516</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.215796975</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>41</v>
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Excellent margin at 24.1% (Team avg: 14.2%)</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>PLUMBING</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>11240</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>3024.41</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.2690756227758007</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>59</v>
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Electricals Dept Head: 74.9% of dept sales, 20.4% margin</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>122640</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>25004.7048</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0.2038870254403131</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales 88% below team average - needs improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Excellent margin at 24.1% (Team avg: 14.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Electricals Dept Head: 74.9% of dept sales, 20.4% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Strong leadership - controls 74.9% of department sales</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Selling across all 4 categories - excellent product range</t>
         </is>
@@ -2200,208 +1779,6 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>WALK IN-BOMAS - General Hardware Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Total Sales</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Total Profit</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Items Sold</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Sales Rank</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>17910</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>2577.2996</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>0.1439028252372976</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>13810</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>1597.0416</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.1156438522809558</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>421.2888</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.16851552</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>558.9692</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.34935575</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales 99% below team average - needs improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  General Hardware: 0.1% of dept, 11.6% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Consider expanding into PLUMBING</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Best margin in ELECTRICALS: 34.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Low contribution at 0.1% of total branch sales - growth opportunity</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2414,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2521,19 +1898,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4467800</v>
+        <v>4485710</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>332272.952</v>
+        <v>334850.2516</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.07437059671426653</v>
+        <v>0.07464821658109864</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>5345.25</v>
+        <v>5398.25</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.2868423172991701</v>
+        <v>0.2879921776113658</v>
       </c>
     </row>
     <row r="6">
@@ -2684,36 +2061,6 @@
       </c>
       <c r="H10" s="10" t="n">
         <v>0.01506856306945291</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>WALK IN-BOMAS</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>General Hardware Team</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>17910</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>2577.2996</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0.1439028252372976</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>0.001149860312195742</v>
       </c>
     </row>
   </sheetData>
@@ -2731,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2824,19 +2171,19 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4340790</v>
+        <v>4354600</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>306511.2428</v>
+        <v>308108.2844</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.07061185701220285</v>
+        <v>0.07075466963670601</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5163.25</v>
+        <v>5183.25</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.3184617721006361</v>
+        <v>0.3194749418399485</v>
       </c>
     </row>
     <row r="8">
@@ -2947,28 +2294,6 @@
       </c>
       <c r="F12" s="10" t="n">
         <v>0.005349404166688065</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>WALK IN-BOMAS</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>13810</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>1597.0416</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>0.1156438522809558</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0.00101316973931238</v>
       </c>
     </row>
   </sheetData>
@@ -2986,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3079,19 +2404,19 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>99250</v>
+        <v>101750</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>17269.442</v>
+        <v>17690.7308</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.1739994156171284</v>
+        <v>0.1738646761670762</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.07410366299819314</v>
+        <v>0.0759702540057043</v>
       </c>
     </row>
     <row r="8">
@@ -3202,28 +2527,6 @@
       </c>
       <c r="F12" s="10" t="n">
         <v>0.01038571236579211</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>WALK IN-BOMAS</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>421.2888</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>0.16851552</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0.001866591007511162</v>
       </c>
     </row>
   </sheetData>
@@ -3474,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3589,19 +2892,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>6220</v>
+        <v>7820</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1910.1488</v>
+        <v>2469.118</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.3070978778135048</v>
+        <v>0.315743989769821</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.03797313797313797</v>
+        <v>0.04774114774114774</v>
       </c>
     </row>
     <row r="9">
@@ -3651,66 +2954,44 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>WALK IN-BOMAS</t>
+          <t>Bonface Muriu</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1600</v>
+        <v>1570</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>558.9692</v>
+        <v>280.198</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.34935575</v>
+        <v>0.1784700636942675</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.009768009768009768</v>
+        <v>0.009584859584859586</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Bonface Muriu</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1570</v>
+        <v>100</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>280.198</v>
+        <v>12.4584</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.1784700636942675</v>
+        <v>0.124584</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.009584859584859586</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>12.4584</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>0.124584</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="10" t="n">
         <v>0.0006105006105006105</v>
       </c>
     </row>
@@ -3729,7 +3010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3799,145 +3080,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Performance Notes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>4971720</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>286100.5324</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.05754558430482812</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>6244</v>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Outstanding! Sales 125% above team average</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>13910</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>2082.0028</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.1496766930265996</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>14</v>
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Margin at 5.9% below team average of 14.2%</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>PLUMBING</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>9910</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>2682.5464</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.2706908577194753</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>8</v>
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  General Hardware: 36.5% of dept, 5.8% margin</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>4450</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>1901.066</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0.4272058426966291</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Outstanding! Sales 157% above team average</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Margin at 5.9% below team average of 14.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  General Hardware: 36.5% of dept, 5.8% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Selling across all 4 categories - excellent product range</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Best margin in ELECTRICALS: 42.7%</t>
         </is>
@@ -3958,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4012,163 +3190,60 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>4467800</v>
+        <v>4485710</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>332272.952</v>
+        <v>334850.2516</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.07437059671426653</v>
+        <v>0.07464821658109864</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>5345.25</v>
+        <v>5398.25</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Performance Notes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>4340790</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>306511.2428</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.07061185701220285</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>5163.25</v>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Outstanding! Sales 102% above team average</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>99250</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>17269.442</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.1739994156171284</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>116</v>
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Margin at 7.5% below team average of 14.2%</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>PLUMBING</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>21540</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>6582.118399999999</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.3055765273909006</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>44</v>
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  General Hardware: 31.9% of dept, 7.1% margin</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>6220</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>1910.1488</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0.3070978778135048</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Outstanding! Sales 129% above team average</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Margin at 7.4% below team average of 14.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  General Hardware: 31.8% of dept, 7.1% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Selling across all 4 categories - excellent product range</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Best margin in ELECTRICALS: 30.7%</t>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Best margin in ELECTRICALS: 31.6%</t>
         </is>
       </c>
     </row>
@@ -4187,7 +3262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4250,145 +3325,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Sales (KES)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Profit (KES)</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Performance Notes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>GENERAL HARDWARE</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>2284585</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>204305.1856</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.0894277015738088</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>2979.75</v>
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales 7% above team average - solid performance</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>PAINTS</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>52800</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>12576.198</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.2381855681818182</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>90</v>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Margin at 9.7% below team average of 14.2%</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PLUMBING</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>29320</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>12255.0636</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.4179762482946793</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>54</v>
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  General Hardware: 16.8% of dept, 8.9% margin</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>ELECTRICALS</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>21000</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>3467.5068</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.1651193714285714</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Performance Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales 23% above team average - solid performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Margin at 9.7% below team average of 14.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  General Hardware: 16.8% of dept, 8.9% margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Selling across all 4 categories - excellent product range</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Best margin in PLUMBING: 41.8%</t>
         </is>
